--- a/docs/downloads/11/tbl_degats_champs_riz_marovoay_bepako.xlsx
+++ b/docs/downloads/11/tbl_degats_champs_riz_marovoay_bepako.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -372,12 +372,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Rien</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Un peu</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Rien</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -394,14 +394,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C2">
-        <v>66.7</v>
+        <v>22.2</v>
       </c>
       <c r="D2">
-        <v>33.3</v>
+        <v>77.8</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -418,17 +418,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -442,68 +442,68 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C4">
-        <v>22.2</v>
+        <v>53.3</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="E4">
-        <v>77.8</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Autres</t>
         </is>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D5">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Autres bestioles</t>
         </is>
       </c>
       <c r="C6">
-        <v>53.3</v>
+        <v>30.8</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>46.2</v>
       </c>
       <c r="E6">
-        <v>13.3</v>
+        <v>23.1</v>
       </c>
       <c r="F6">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -514,20 +514,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Criquets</t>
         </is>
       </c>
       <c r="C7">
-        <v>84.59999999999999</v>
+        <v>17.6</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F7">
-        <v>15.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -538,17 +538,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="C8">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>23.1</v>
+        <v>75</v>
       </c>
       <c r="E8">
-        <v>46.2</v>
+        <v>25</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -562,17 +562,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Criquets</t>
+          <t>Facteur humain</t>
         </is>
       </c>
       <c r="C9">
-        <v>17.6</v>
+        <v>3.8</v>
       </c>
       <c r="D9">
-        <v>70.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E9">
-        <v>11.8</v>
+        <v>23.1</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -586,17 +586,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Inondation</t>
         </is>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E10">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -610,17 +610,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C11">
-        <v>3.8</v>
+        <v>9.5</v>
       </c>
       <c r="D11">
-        <v>23.1</v>
+        <v>90.5</v>
       </c>
       <c r="E11">
-        <v>73.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -634,17 +634,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inondation</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C12">
-        <v>40</v>
+        <v>22.9</v>
       </c>
       <c r="D12">
-        <v>40</v>
+        <v>5.7</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -658,67 +658,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C13">
-        <v>9.5</v>
+        <v>66.5</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="E13">
-        <v>90.5</v>
+        <v>17.4</v>
       </c>
       <c r="F13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Rats</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>22.9</v>
-      </c>
-      <c r="D14">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="E14">
-        <v>5.7</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Sécheresse</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>66.5</v>
-      </c>
-      <c r="D15">
-        <v>17.4</v>
-      </c>
-      <c r="E15">
-        <v>3.6</v>
-      </c>
-      <c r="F15">
         <v>12.5</v>
       </c>
     </row>
